--- a/output/(山本)保守性_再利用性_再構成.xlsx
+++ b/output/(山本)保守性_再利用性_再構成.xlsx
@@ -461,13 +461,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ソフトウェアの構成要素(クラス、関数、コンポーネント等)と設計書の章節を1対1で対応させ、各要素の役割や境界を独立したモジュールとして定義することで、特定の設計単位を単独で参照または再利用できる構造にしていること。</t>
+          <t>共通機能やロジック設計を、システム全体から独立して参照可能なモジュールや関数の単位に分離し、単独の設計書として文書化している。</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>【非適合例】一連の業務プロセスが単一の長大な文章で記述されており、特定の計算ロジックのみを抽出して再利用することが困難である。(設計文書で再利用可能な部品が分離されていない)。
-→【適合例】計算ロジックやデータ変換処理を関数単位の節に分割し、それぞれの入出力仕様と処理内容を独立した単位として定義している。</t>
+          <t>★新規追加
+【非適合例】画面Aの設計書内に、日付フォーマットのチェック処理の詳細が直接記述されている。（共通処理が部品化されていないため、仕様変更時の影響範囲が特定しにくい。）
+→【適合例】日付フォーマットのチェック処理を、共通関数「DateValidator」の設計書として独立して記述し、画面Aの設計書からは当該関数名を参照する構成にしている。</t>
         </is>
       </c>
     </row>
@@ -479,14 +480,14 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>システム全体で共通利用されるビジネスロジック、バリデーションルール、またはエラーハンドリングを共通仕様として外部化し、各機能からはその定義を一意の識別子等で参照する形式をとることで、情報の冗長性を排除していること。</t>
+          <t>エラーハンドリングやログ出力などの横断的関心事を個別の機能設計から分離し、共通仕様書において異常の種類や事象ごとに独立した項目として定義している。</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】画面ごとに同一の入力チェックルールが個別に記述されており、仕様変更時に修正漏れが発生するリスクがある。(共通部品として集約されていない)。
-→【適合例】「共通バリデーション定義」を個別に設け、各画面の設計書からは当該定義のIDを参照することで、仕様の一元管理と再利用性を実現している。</t>
+【非適合例】各APIの設計書ごとに、ネットワークタイムアウト時のリトライ処理が別々の書式で記載されている。（異常時の動作が機能単位で分散しており、システム全体の統一性が担保されていない。）
+→【適合例】共通仕様書の「異常時の共通動作」章において、ネットワークタイムアウト時のリトライ回数および間隔を一元的に定義し、各APIの設計書からは当該章を参照させている。</t>
         </is>
       </c>
     </row>
@@ -498,32 +499,33 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>ドキュメントの網羅性と検索性を確保するため、対象文書ごとに論理構成（章立て）を規定した標準テンプレート、および図解の表記法や配置を定めたフォーマットを策定し、プロジェクト全体で一貫して適用していること。</t>
+          <t>成果物の構成要素および記載粒度を均一にするため、プロジェクト計画書等で合意された指定のテンプレートやフォーマットに準拠してドキュメントを記述している。</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>【非適合例】作成者によって設計書の構成やUML図の表記方法が異なり、必要な情報の特定に時間を要している。(標準テンプレートやフォーマットが適用されていない)。
-→【適合例】プロジェクト標準の設計書テンプレートを適用し、すべての文書において目次構成や図表の記述スタイルが統一されている。</t>
+          <t>★新規追加
+【非適合例】基本設計書において、担当者Aはワープロソフトのフリーフォーマットで、担当者Bは表計算ソフトの表形式で画面仕様を記述している。（フォーマットが統一されておらず、記載粒度にばらつきが生じている。）
+→【適合例】基本設計書において、すべての画面仕様をプロジェクト管理標準で指定された「画面設計書テンプレート」に準拠して記述している。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>記述 de 基準または標準を定めている</t>
+          <t>記述の基準または標準を定めている</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>表記揺れによる誤解や可読性の低下を防ぐため、外来語の長音有無、算用数字の使用基準、特殊記号の扱い、および技術用語の採用基準を明記した執筆ガイドラインを策定し、それに従って記述していること。</t>
+          <t>文書全体の表記揺れを防ぐため、「JTF日本語標準スタイルガイド」などの公的なガイドライン、またはプロジェクト固有の用字用語ルールに準拠して記述している。</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】同一文書内で「ユーザ」と「ユーザー」が混在し、数値表記も全角と半角が入り混じっている。(表記ルールが定義または適用されていない)。
-→【適合例】プロジェクト別のスタイルガイドに従い、外来語の末尾長音を省略せず、数字はすべて半角に統一して記述している。</t>
+【非適合例】同一の基本設計書内で、「サーバー」「サーバ」および「ユーザー」「ユーザ」という表記が混在している。（用字用語の基準が定められておらず、検索性や可読性が低下している。）
+→【適合例】プロジェクトの用字用語ルールとして「JTF日本語標準スタイルガイド」の適用を明記し、長音符の付与基準を「サーバー」「ユーザー」に統一して記述している。</t>
         </is>
       </c>
     </row>
@@ -535,13 +537,14 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>ドメイン固有の専門用語や多義的な単語による認識齟齬を排除するため、名称、定義、および別名を網羅したプロジェクト用語集またはデータディクショナリを整備し、すべての文書においてその定義を遵守していること。</t>
+          <t>開発関係者間におけるドメイン知識の解釈のブレを防ぐため、プロジェクト内で使用する業務用語やシステム用語を網羅した用語集を独立した文書または章として作成している。</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>【非適合例】「案件」という単語が、ある箇所では「商談」を指し、別の箇所では「作業タスク」を指している。(用語集がなく、文脈によって用語の意味が揺れている)。
-→【適合例】プロジェクト共通の用語集において「案件」を「成約前の営業活動単位」と一義的に定義し、システム全体の設計記述でこの定義を統一して使用している。</t>
+          <t>★新規追加
+【非適合例】要件定義書において、同一の利用者を指す言葉として「顧客」「ユーザー」「アカウント」が明確な定義なく混在している。（用語の定義が文書化されておらず、仕様誤認を誘発する状態である。）
+→【適合例】要件定義書の冒頭に用語定義の章を設け、「顧客：サービスを利用するエンドユーザー」「アカウント：システム上の認証情報」のように用語の意味を明記している。</t>
         </is>
       </c>
     </row>
@@ -553,14 +556,14 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>既存資産の保守性と継続性を損なわないよう、派生開発や機能追加の着手前に旧システムの用語体系を調査し、新規追加用語との衝突回避や意味的整合性を担保した更新版の用語集を維持していること。</t>
+          <t>既存システムを改修する派生開発において、既存仕様の誤認を防ぐため、派生元システム固有の略語や専門用語を抽出した用語集を開発着手前に作成し、すべての設計書から参照可能にしている。</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】派生開発において、既存システムで「受注番号」と定義されていた項目を、既存ドキュメントを確認せずに「オーダーID」と新しく命名して定義している。(派生元との整合性が考慮されていない)。
-→【適合例】既存のデータディクショナリを継承し、追加機能で必要となる用語のみを既存の命名規約に合わせて定義することで、システム全体で一貫した用語体系を維持している。</t>
+【非適合例】派生開発の設計書において、レガシーシステム特有の略語である「TMT」が、何の説明もなく使用されている。（派生元システム固有の用語定義が存在せず、新規参画者の理解を阻害している。）
+→【適合例】派生開発の要件定義工程において、派生元の既存ドキュメントから「TMT（トランザクション管理テーブル）」などの特有語彙を抽出して用語集を作成し、各設計書から参照可能にしている。</t>
         </is>
       </c>
     </row>
